--- a/Data/Home/BedroomTwo.Temperature.xlsx
+++ b/Data/Home/BedroomTwo.Temperature.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:I219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709236478</v>
+        <v>1711833627</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709260821</v>
+        <v>1711858455</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709264347</v>
+        <v>1711864811</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709274631</v>
+        <v>1711891311</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -593,10 +601,11 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709278555</v>
+        <v>1711893315</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709287158</v>
+        <v>1711896170</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709291656</v>
+        <v>1711900868</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +704,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709247153</v>
+        <v>1711901979</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -721,10 +733,15 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Comfortable</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +760,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709252814</v>
+        <v>1711903189</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -753,10 +770,11 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +793,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709256616</v>
+        <v>1711904404</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -785,10 +803,15 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +830,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709265646</v>
+        <v>1711905567</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -817,10 +840,11 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +863,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709276268</v>
+        <v>1711906720</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -849,10 +873,15 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Comfortable</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +900,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709284972</v>
+        <v>1711909027</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +914,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +933,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709332800</v>
+        <v>1711909838</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -913,10 +943,15 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Comfortable</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +970,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709343336</v>
+        <v>1711912165</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -945,10 +980,11 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +1003,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709348761</v>
+        <v>1711912969</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -977,10 +1013,15 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1040,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709354471</v>
+        <v>1711915368</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1009,10 +1050,11 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1073,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709369055</v>
+        <v>1711916164</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1041,10 +1083,15 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Comfortable</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1110,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709408376</v>
+        <v>1711918456</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1124,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1143,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709418709</v>
+        <v>1711919254</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1105,10 +1153,15 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Comfortable</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1180,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709428675</v>
+        <v>1711921581</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1137,10 +1190,11 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1213,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709434097</v>
+        <v>1711922384</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1169,10 +1223,15 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1250,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709448528</v>
+        <v>1711924712</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1201,10 +1260,11 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1283,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709456464</v>
+        <v>1711925531</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1233,10 +1293,15 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Comfortable</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1320,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709511698</v>
+        <v>1711927963</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1265,10 +1330,11 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1353,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709515064</v>
+        <v>1711928770</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1297,10 +1363,15 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1390,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709535825</v>
+        <v>1711930826</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1329,10 +1400,11 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1423,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709544674</v>
+        <v>1711931605</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1361,10 +1433,15 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Comfortable</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1460,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709574182</v>
+        <v>1711933051</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1474,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1493,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709586805</v>
+        <v>1711933858</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1425,10 +1503,15 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Comfortable</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1530,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709598155</v>
+        <v>1711935276</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1457,10 +1540,11 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1563,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709602459</v>
+        <v>1711936771</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1489,10 +1573,15 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1600,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709615974</v>
+        <v>1711937461</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1521,10 +1610,11 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1633,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709626612</v>
+        <v>1711939077</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1553,10 +1643,15 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Comfortable</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1670,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709636255</v>
+        <v>1711939811</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1684,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1703,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709655188</v>
+        <v>1711953253</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1717,7 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1736,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709661222</v>
+        <v>1711954120</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1750,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1769,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709673993</v>
+        <v>1711955462</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1783,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1802,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709687077</v>
+        <v>1711956339</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1713,10 +1812,11 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1835,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709711925</v>
+        <v>1711957581</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1849,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1868,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709716724</v>
+        <v>1711958510</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1882,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1901,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709759269</v>
+        <v>1711959690</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1915,7 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1934,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709771185</v>
+        <v>1711960499</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1841,10 +1944,11 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1967,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709780693</v>
+        <v>1711961808</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1873,10 +1977,11 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +2000,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709790810</v>
+        <v>1711962491</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1905,10 +2010,11 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +2033,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709793037</v>
+        <v>1711963687</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +2047,7 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2066,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709798610</v>
+        <v>1711964562</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2080,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2099,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709801645</v>
+        <v>1711966472</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2113,7 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2132,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709834766</v>
+        <v>1711967676</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2033,10 +2142,11 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Cold</t>
+          <t>BedroomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2165,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709843691</v>
+        <v>1711978333</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2179,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2198,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709856356</v>
+        <v>1712000876</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2097,10 +2208,11 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2231,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709859422</v>
+        <v>1712024908</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2129,10 +2241,11 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2264,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709864893</v>
+        <v>1712029466</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2278,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2297,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709868343</v>
+        <v>1712041267</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2311,11 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2334,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709873131</v>
+        <v>1712052219</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2348,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2367,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709878846</v>
+        <v>1712052513</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2381,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2400,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709884731</v>
+        <v>1712053134</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2414,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2433,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709918617</v>
+        <v>1712057921</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2447,7 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2466,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709923145</v>
+        <v>1712060443</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2353,10 +2476,11 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Cold</t>
+          <t>BedroomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2499,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709937968</v>
+        <v>1712074479</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2513,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2532,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709945945</v>
+        <v>1712086608</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2417,10 +2542,11 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2565,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709949743</v>
+        <v>1712111336</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2449,10 +2575,11 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2598,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709960703</v>
+        <v>1712115128</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2612,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2631,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709978620</v>
+        <v>1712127256</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2513,10 +2641,15 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Comfortable</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2668,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709983329</v>
+        <v>1712140726</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2545,10 +2678,11 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Cold</t>
+          <t>BedroomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2701,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710023320</v>
+        <v>1712154636</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2715,7 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2734,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710030458</v>
+        <v>1712172468</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2609,10 +2744,11 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2767,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710034217</v>
+        <v>1712196057</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2641,10 +2777,11 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2800,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710039310</v>
+        <v>1712200885</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2814,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2833,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710043227</v>
+        <v>1712212757</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2847,11 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2870,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710049362</v>
+        <v>1712226558</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2884,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2903,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710057104</v>
+        <v>1712233450</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2917,7 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2936,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710092615</v>
+        <v>1712239194</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2801,10 +2946,11 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Cold</t>
+          <t>BedroomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2969,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710109301</v>
+        <v>1712253692</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +2983,7 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +3002,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710116699</v>
+        <v>1712262052</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2865,10 +3012,11 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3035,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710120347</v>
+        <v>1712282816</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2897,10 +3045,11 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3068,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710138060</v>
+        <v>1712287928</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3082,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3101,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710142193</v>
+        <v>1712300435</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2961,10 +3111,15 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Comfortable</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3138,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710183337</v>
+        <v>1712315085</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2993,10 +3148,11 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Cold</t>
+          <t>BedroomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3171,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710200035</v>
+        <v>1712323954</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3185,7 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3204,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710211833</v>
+        <v>1712345982</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3057,10 +3214,11 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3237,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710238294</v>
+        <v>1712373701</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3251,7 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3270,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710268559</v>
+        <v>1712380804</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3121,10 +3280,11 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Cold</t>
+          <t>BedroomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3303,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710279695</v>
+        <v>1712406574</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3317,7 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3336,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710293693</v>
+        <v>1712432710</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3185,10 +3346,11 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3369,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710316672</v>
+        <v>1712460635</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3383,7 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3402,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710324271</v>
+        <v>1712468999</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3249,10 +3412,11 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Cold</t>
+          <t>BedroomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3435,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710361692</v>
+        <v>1712479832</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3281,10 +3445,15 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Comfortable</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3472,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710382959</v>
+        <v>1712494140</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3486,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3505,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710403263</v>
+        <v>1712502740</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3519,7 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3538,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710413287</v>
+        <v>1712524514</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3552,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3571,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710450294</v>
+        <v>1712546418</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3585,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3604,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710466060</v>
+        <v>1712553997</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3618,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3637,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710469890</v>
+        <v>1712578548</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3473,10 +3647,11 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3670,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710483251</v>
+        <v>1712585015</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3684,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3703,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710494499</v>
+        <v>1712598995</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3717,7 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3736,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710528501</v>
+        <v>1712607316</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3750,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3769,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710542997</v>
+        <v>1712628448</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3783,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3802,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710551645</v>
+        <v>1712633057</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3816,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3835,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710576341</v>
+        <v>1712647112</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3665,10 +3845,15 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Comfortable</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3872,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710612928</v>
+        <v>1712664567</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3697,10 +3882,11 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Cold</t>
+          <t>BedroomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3905,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710626252</v>
+        <v>1712685096</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3919,7 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3938,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710634199</v>
+        <v>1712693571</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3761,10 +3948,11 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3971,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710637821</v>
+        <v>1712715815</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3793,10 +3981,11 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +4004,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710650658</v>
+        <v>1712720096</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +4018,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4037,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710659122</v>
+        <v>1712732584</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3857,10 +4047,15 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Comfortable</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4074,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710666449</v>
+        <v>1712750075</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3889,10 +4084,11 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Cold</t>
+          <t>BedroomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4107,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710673675</v>
+        <v>1712762465</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4121,7 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4140,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710698789</v>
+        <v>1712778462</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4154,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4173,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710709881</v>
+        <v>1712801632</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3989,6 +4187,7 @@
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4206,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710722969</v>
+        <v>1712805628</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4220,7 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4239,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710726538</v>
+        <v>1712817706</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4253,11 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4276,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710746068</v>
+        <v>1712831816</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4290,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4309,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710751632</v>
+        <v>1712852813</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4117,6 +4323,7 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4342,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710785086</v>
+        <v>1712858358</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4356,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4375,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710800373</v>
+        <v>1712886330</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4389,7 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4408,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710809845</v>
+        <v>1712890949</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4422,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4441,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710813744</v>
+        <v>1712903600</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4455,11 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4478,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710827004</v>
+        <v>1712919174</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4492,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4511,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710837065</v>
+        <v>1712926702</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4525,7 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4544,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710842414</v>
+        <v>1712950571</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4558,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4577,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710866804</v>
+        <v>1712978228</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4591,7 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4610,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710870939</v>
+        <v>1712984865</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4401,10 +4620,11 @@
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Cold</t>
+          <t>BedroomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4643,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710883519</v>
+        <v>1713010832</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4657,7 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4676,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710894164</v>
+        <v>1713031060</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4465,10 +4686,11 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4709,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710918860</v>
+        <v>1713060911</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4501,6 +4723,7 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4742,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710921322</v>
+        <v>1713063940</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4529,10 +4752,11 @@
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Cold</t>
+          <t>BedroomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4775,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710932751</v>
+        <v>1713075721</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4561,10 +4785,15 @@
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Comfortable</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4812,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710964434</v>
+        <v>1713091494</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4593,10 +4822,11 @@
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Cold</t>
+          <t>BedroomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4845,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710974895</v>
+        <v>1713101350</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +4859,7 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4878,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710987424</v>
+        <v>1713127865</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4657,10 +4888,11 @@
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4911,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1711010401</v>
+        <v>1713150439</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +4925,7 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4944,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1711019071</v>
+        <v>1713158415</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4721,10 +4954,11 @@
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Cold</t>
+          <t>BedroomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4977,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1711057863</v>
+        <v>1713177244</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +4991,7 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +5010,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1711068449</v>
+        <v>1713183966</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4785,10 +5020,11 @@
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +5043,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1711072434</v>
+        <v>1713186086</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4817,10 +5053,11 @@
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5076,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1711074964</v>
+        <v>1713235652</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4853,6 +5090,7 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5109,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1711095012</v>
+        <v>1713239544</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4881,10 +5119,15 @@
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Comfortable</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5146,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1711098762</v>
+        <v>1713268194</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4913,10 +5156,11 @@
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Cold</t>
+          <t>BedroomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5179,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1711130814</v>
+        <v>1713277117</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4945,10 +5189,11 @@
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: ExcessivelyCold</t>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5212,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1711134498</v>
+        <v>1713296753</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4981,6 +5226,7 @@
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5245,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1711144667</v>
+        <v>1713321050</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5013,6 +5259,7 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5278,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1711153540</v>
+        <v>1713325445</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5045,6 +5292,7 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5311,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1711157181</v>
+        <v>1713338326</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5077,6 +5325,11 @@
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5348,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1711168482</v>
+        <v>1713352048</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5109,6 +5362,7 @@
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5381,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1711181263</v>
+        <v>1713372544</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5141,6 +5395,7 @@
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5414,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1711184837</v>
+        <v>1713387860</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5173,6 +5428,7 @@
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5447,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1711213256</v>
+        <v>1713410056</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5205,6 +5461,7 @@
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5480,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1711218416</v>
+        <v>1713417881</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5233,10 +5490,11 @@
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Cold</t>
+          <t>BedroomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5513,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1711233029</v>
+        <v>1713440991</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5269,6 +5527,7 @@
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5546,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1711243608</v>
+        <v>1713441387</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5297,10 +5556,11 @@
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5579,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1711247434</v>
+        <v>1713442450</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5329,10 +5589,15 @@
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5616,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1711252381</v>
+        <v>1713446157</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5361,10 +5626,11 @@
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5649,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1711258892</v>
+        <v>1713454530</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5393,10 +5659,11 @@
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5682,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1711264771</v>
+        <v>1713470247</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5425,10 +5692,11 @@
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5715,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1711272361</v>
+        <v>1713493358</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5461,6 +5729,7 @@
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5748,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1711301442</v>
+        <v>1713497360</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5489,10 +5758,11 @@
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Cold</t>
+          <t>BedroomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5781,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1711321373</v>
+        <v>1713509121</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5521,10 +5791,15 @@
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Comfortable</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5818,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1711328705</v>
+        <v>1713524100</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5557,6 +5832,7 @@
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5851,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1711332683</v>
+        <v>1713532713</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5585,10 +5861,11 @@
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5884,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1711338871</v>
+        <v>1713556644</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5617,10 +5894,11 @@
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Warm</t>
+          <t>BedroomTwo.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +5917,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1711351733</v>
+        <v>1713585185</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5649,10 +5927,11 @@
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +5950,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1711354241</v>
+        <v>1713593517</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5685,6 +5964,7 @@
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +5983,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1711357373</v>
+        <v>1713604327</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5713,10 +5993,15 @@
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Comfortable</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +6020,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1711361437</v>
+        <v>1713620233</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5745,10 +6030,11 @@
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Cold</t>
+          <t>BedroomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +6053,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1711368695</v>
+        <v>1713629371</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5781,6 +6067,7 @@
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +6086,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1711390115</v>
+        <v>1713642258</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5813,6 +6100,7 @@
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6119,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1711398985</v>
+        <v>1713668300</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5845,6 +6133,7 @@
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6152,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1711419564</v>
+        <v>1713676990</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5877,6 +6166,7 @@
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6185,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1711424141</v>
+        <v>1713685862</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5909,6 +6199,11 @@
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6222,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1711443607</v>
+        <v>1713699813</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5941,6 +6236,7 @@
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6255,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1711453028</v>
+        <v>1713708502</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5973,6 +6269,7 @@
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6288,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1711462442</v>
+        <v>1713728323</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6005,6 +6302,7 @@
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6321,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1711469064</v>
+        <v>1713751406</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6037,6 +6335,7 @@
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6055,7 +6354,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1711476573</v>
+        <v>1713755492</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6065,10 +6364,11 @@
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Cold</t>
+          <t>BedroomTwo.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6087,7 +6387,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1711486101</v>
+        <v>1713767785</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6097,10 +6397,15 @@
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr">
         <is>
-          <t>BedroomTwo.Temperature.state: Comfortable</t>
+          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6119,7 +6424,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1711525041</v>
+        <v>1713781753</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6133,6 +6438,7 @@
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6151,7 +6457,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1711540008</v>
+        <v>1713788115</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6165,6 +6471,7 @@
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6183,7 +6490,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1711552226</v>
+        <v>1713814629</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6197,6 +6504,7 @@
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6215,7 +6523,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1711558115</v>
+        <v>1713838288</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6229,6 +6537,7 @@
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6247,7 +6556,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1711613476</v>
+        <v>1713842473</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6261,6 +6570,7 @@
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6279,7 +6589,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1711624678</v>
+        <v>1713855503</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6289,10 +6599,1219 @@
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
+          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1713869578</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>1713876709</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
           <t>BedroomTwo.Temperature.state: Comfortable</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>1713905658</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>1713927804</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>1713935789</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>1713953288</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>1713953770</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>1713956024</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: ExcessivelyCold</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>1713956738</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>1713957953</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>1713998666</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>1714015343</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>1714022246</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>1714046342</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>1714047930</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>1714050720</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>1714067518</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>1714097017</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>1714101246</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>1714114423</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>1714130361</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>1714138123</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>1714146577</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>1714149532</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>1714153909</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>1714184544</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>1714188294</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>1714202097</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>1714217041</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>1714226054</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>1714247574</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>1714275904</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>1714284323</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>1714294178</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: ExcessivelyHot</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>1714310229</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>1714320248</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
